--- a/artfynd/A 34163-2026 artfynd.xlsx
+++ b/artfynd/A 34163-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1968,48 +1968,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66501943</v>
+        <v>137504209</v>
       </c>
       <c r="B14" t="n">
-        <v>93201</v>
+        <v>93486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gålberget, Jmt</t>
+          <t>Galberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435973</v>
+        <v>435877</v>
       </c>
       <c r="R14" t="n">
-        <v>6966943</v>
+        <v>6967007</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,74 +2049,73 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>14673</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66501943</t>
+          <t>https://artportalen.se/Sighting/137504209</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66501935</v>
+        <v>137504210</v>
       </c>
       <c r="B15" t="n">
-        <v>91872</v>
+        <v>93486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gålberget, Jmt</t>
+          <t>Galberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436020</v>
+        <v>435973</v>
       </c>
       <c r="R15" t="n">
-        <v>6966903</v>
+        <v>6967202</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,12 +2139,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,74 +2155,73 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>14666</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66501935</t>
+          <t>https://artportalen.se/Sighting/137504210</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66502088</v>
+        <v>137504213</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>93486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gålberget, Jmt</t>
+          <t>Galberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436207</v>
+        <v>436108</v>
       </c>
       <c r="R16" t="n">
-        <v>6967357</v>
+        <v>6967362</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,12 +2245,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,36 +2261,35 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>14802</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66502088</t>
+          <t>https://artportalen.se/Sighting/137504213</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66501934</v>
+        <v>137504225</v>
       </c>
       <c r="B17" t="n">
-        <v>79946</v>
+        <v>93486</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,37 +2297,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gålberget, Jmt</t>
+          <t>Galberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436020</v>
+        <v>435967</v>
       </c>
       <c r="R17" t="n">
-        <v>6966903</v>
+        <v>6967198</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2354,12 +2351,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,58 +2367,57 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>14665</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66501934</t>
+          <t>https://artportalen.se/Sighting/137504225</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66501939</v>
+        <v>66501943</v>
       </c>
       <c r="B18" t="n">
-        <v>79946</v>
+        <v>93201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436015</v>
+        <v>435973</v>
       </c>
       <c r="R18" t="n">
-        <v>6966924</v>
+        <v>6966943</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2480,7 +2476,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2497,38 +2493,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66501939</t>
+          <t>https://artportalen.se/Sighting/66501943</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66501947</v>
+        <v>66501935</v>
       </c>
       <c r="B19" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435975</v>
+        <v>436020</v>
       </c>
       <c r="R19" t="n">
-        <v>6966966</v>
+        <v>6966903</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2587,7 +2583,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2604,38 +2600,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66501947</t>
+          <t>https://artportalen.se/Sighting/66501935</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66501950</v>
+        <v>66502088</v>
       </c>
       <c r="B20" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436000</v>
+        <v>436207</v>
       </c>
       <c r="R20" t="n">
-        <v>6966984</v>
+        <v>6967357</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2694,7 +2690,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2711,54 +2707,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66501950</t>
+          <t>https://artportalen.se/Sighting/66502088</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>91841163</v>
+        <v>137504217</v>
       </c>
       <c r="B21" t="n">
-        <v>57141</v>
+        <v>93524</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Galberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436069</v>
+        <v>435965</v>
       </c>
       <c r="R21" t="n">
-        <v>6967273</v>
+        <v>6967190</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2782,12 +2778,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2802,31 +2798,31 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91841163</t>
+          <t>https://artportalen.se/Sighting/137504217</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>66501951</v>
+        <v>66501934</v>
       </c>
       <c r="B22" t="n">
-        <v>58057</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,21 +2830,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2858,10 +2854,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436015</v>
+        <v>436020</v>
       </c>
       <c r="R22" t="n">
-        <v>6966990</v>
+        <v>6966903</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2907,7 +2903,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2924,51 +2920,51 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66501951</t>
+          <t>https://artportalen.se/Sighting/66501934</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>91953913</v>
+        <v>66501939</v>
       </c>
       <c r="B23" t="n">
-        <v>104628</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Gålberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435925</v>
+        <v>436015</v>
       </c>
       <c r="R23" t="n">
-        <v>6967077</v>
+        <v>6966924</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2995,12 +2991,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3011,66 +3007,71 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>14670</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91953913</t>
+          <t>https://artportalen.se/Sighting/66501939</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>91953915</v>
+        <v>66501947</v>
       </c>
       <c r="B24" t="n">
-        <v>99038</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223597</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Gålberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435925</v>
+        <v>435975</v>
       </c>
       <c r="R24" t="n">
-        <v>6967077</v>
+        <v>6966966</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3097,12 +3098,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3113,66 +3114,71 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>14677</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91953915</t>
+          <t>https://artportalen.se/Sighting/66501947</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>91953927</v>
+        <v>66501950</v>
       </c>
       <c r="B25" t="n">
-        <v>99038</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223597</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Gålberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435950</v>
+        <v>436000</v>
       </c>
       <c r="R25" t="n">
-        <v>6967175</v>
+        <v>6966984</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3199,12 +3205,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,73 +3221,74 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>14680</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91953927</t>
+          <t>https://artportalen.se/Sighting/66501950</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>66501937</v>
+        <v>91841163</v>
       </c>
       <c r="B26" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gålberget, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436015</v>
+        <v>436069</v>
       </c>
       <c r="R26" t="n">
-        <v>6966924</v>
+        <v>6967273</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3305,12 +3312,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,36 +3328,35 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>14668</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66501937</t>
+          <t>https://artportalen.se/Sighting/91841163</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>66501949</v>
+        <v>66501951</v>
       </c>
       <c r="B27" t="n">
-        <v>79917</v>
+        <v>58057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3382,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436000</v>
+        <v>436015</v>
       </c>
       <c r="R27" t="n">
-        <v>6966984</v>
+        <v>6966990</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3431,7 +3437,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3448,54 +3454,54 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66501949</t>
+          <t>https://artportalen.se/Sighting/66501951</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>66502081</v>
+        <v>137504208</v>
       </c>
       <c r="B28" t="n">
-        <v>79917</v>
+        <v>108213</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>219933</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gålberget, Jmt</t>
+          <t>Galberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436028</v>
+        <v>435968</v>
       </c>
       <c r="R28" t="n">
-        <v>6967188</v>
+        <v>6967193</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3519,12 +3525,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3535,27 +3541,763 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>14795</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504208</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>91953913</v>
+      </c>
+      <c r="B29" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>435925</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6967077</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953913</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>91953915</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>435925</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6967077</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953915</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>91953927</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>435950</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6967175</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953927</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>66501937</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gålberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>436015</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6966924</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2013-05-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2013-05-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>14668</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
           <t>Malin Sahlin</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>Via Malin Sahlin</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr">
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501937</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>66501949</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gålberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>436000</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6966984</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2013-05-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2013-05-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>14679</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501949</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>66502081</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gålberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>436028</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6967188</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2013-05-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2013-05-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>14795</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66502081</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137504214</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80126</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Galberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>435941</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6967116</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504214</t>
         </is>
       </c>
     </row>
@@ -3588,6 +4330,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34163-2026 artfynd.xlsx
+++ b/artfynd/A 34163-2026 artfynd.xlsx
@@ -1971,7 +1971,7 @@
         <v>137504209</v>
       </c>
       <c r="B14" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>137504210</v>
       </c>
       <c r="B15" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>137504213</v>
       </c>
       <c r="B16" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137504225</v>
       </c>
       <c r="B17" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137504217</v>
       </c>
       <c r="B21" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>137504208</v>
       </c>
       <c r="B28" t="n">
-        <v>108213</v>
+        <v>108217</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>137504214</v>
       </c>
       <c r="B35" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
